--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.70689020828901</v>
+        <v>11.00236965884696</v>
       </c>
       <c r="D2" t="n">
-        <v>25.15493226871437</v>
+        <v>4.087676493666086</v>
       </c>
       <c r="E2" t="n">
-        <v>23.47686184355826</v>
+        <v>3.814990049578217</v>
       </c>
       <c r="F2" t="n">
-        <v>32.54251838113257</v>
+        <v>5.288159236934042</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.09096268424156</v>
+        <v>10.41478143618925</v>
       </c>
       <c r="D3" t="n">
-        <v>100.0613104503722</v>
+        <v>16.25996294818548</v>
       </c>
       <c r="E3" t="n">
-        <v>23.47686184355826</v>
+        <v>3.814990049578217</v>
       </c>
       <c r="F3" t="n">
-        <v>32.54251838113257</v>
+        <v>5.288159236934042</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.78089626705524</v>
+        <v>9.389395643396476</v>
       </c>
       <c r="D4" t="n">
-        <v>68.89213302250511</v>
+        <v>11.19497161615708</v>
       </c>
       <c r="E4" t="n">
-        <v>23.47686184355826</v>
+        <v>3.814990049578217</v>
       </c>
       <c r="F4" t="n">
-        <v>32.54251838113257</v>
+        <v>5.288159236934042</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.79316241785331</v>
+        <v>2.403888892901163</v>
       </c>
       <c r="D5" t="n">
-        <v>16.35658033185985</v>
+        <v>2.657944303927226</v>
       </c>
       <c r="E5" t="n">
-        <v>23.47686184355826</v>
+        <v>3.814990049578217</v>
       </c>
       <c r="F5" t="n">
-        <v>32.54251838113257</v>
+        <v>5.288159236934042</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.66114917175152</v>
+        <v>2.707436740409622</v>
       </c>
       <c r="D6" t="n">
-        <v>22.82001929905046</v>
+        <v>3.7082531360957</v>
       </c>
       <c r="E6" t="n">
-        <v>23.47686184355826</v>
+        <v>3.814990049578217</v>
       </c>
       <c r="F6" t="n">
-        <v>32.54251838113257</v>
+        <v>5.288159236934042</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
